--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY137"/>
+  <dimension ref="A1:AZ137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106169491</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156909</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -992,6 +1007,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159887</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128777823</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1313,6 +1343,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128777841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778043</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1527,6 +1567,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778161</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1653,6 +1698,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129087677</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1779,6 +1829,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129087792</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1889,6 +1944,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103818406</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1996,6 +2056,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778003</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2102,6 +2167,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132270844</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126426449</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2331,6 +2406,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88473654</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2440,6 +2520,11 @@
       <c r="AY17" t="inlineStr">
         <is>
           <t>Dalaflorans databas</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62380541</t>
         </is>
       </c>
     </row>
@@ -2548,6 +2633,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83064279</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2668,6 +2758,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117254</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2788,6 +2883,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117394</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2928,6 +3028,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103794269</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3055,6 +3160,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103794360</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3190,6 +3300,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103794382</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3311,6 +3426,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285436</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3419,6 +3539,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108697481</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3527,6 +3652,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108697582</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3629,6 +3759,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108723777</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3726,6 +3861,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108861549</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3823,6 +3963,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108861553</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3925,6 +4070,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888938</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4027,6 +4177,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888939</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157436</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4241,6 +4401,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157615</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4357,6 +4522,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157771</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4464,6 +4634,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159146</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4571,6 +4746,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159285</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4687,6 +4867,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128777833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4794,6 +4979,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128777939</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4915,6 +5105,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778094</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5035,6 +5230,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972696</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5159,6 +5359,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972812</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5283,6 +5488,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132972876</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5403,6 +5613,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132973018</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5522,6 +5737,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117363</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5629,6 +5849,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159363</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5735,6 +5960,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879770</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5836,6 +6066,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879780</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5970,6 +6205,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117215</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6104,6 +6344,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117226</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6238,6 +6483,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117237</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6372,6 +6622,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117243</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6491,6 +6746,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117370</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6599,6 +6859,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285324</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6733,6 +6998,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880509</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6867,6 +7137,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880532</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6974,6 +7249,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156808</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7089,6 +7369,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88473675</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7219,6 +7504,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129087756</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7353,6 +7643,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103794366</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7487,6 +7782,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103794376</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7621,6 +7921,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880484</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7755,6 +8060,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880562</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7889,6 +8199,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880574</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8023,6 +8338,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880580</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8157,6 +8477,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880591</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8254,6 +8579,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909020</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8351,6 +8681,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909299</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8458,6 +8793,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156316</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8565,6 +8905,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156348</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8672,6 +9017,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120156715</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8782,6 +9132,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720293</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8892,6 +9247,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720315</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8997,6 +9357,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128100875</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9102,6 +9467,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128100995</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9207,6 +9577,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101334</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9313,6 +9688,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879766</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9427,6 +9807,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879772</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9528,6 +9913,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879773</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9629,6 +10019,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879774</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9730,6 +10125,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879775</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9831,6 +10231,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879776</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9932,6 +10337,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879778</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10033,6 +10443,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82879779</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10144,6 +10559,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117272</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10255,6 +10675,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117403</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10363,6 +10788,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285212</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10460,6 +10890,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909310</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10579,6 +11014,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133055708</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10690,6 +11130,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117320</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10816,6 +11261,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82056722</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10913,6 +11363,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119909303</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11052,6 +11507,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880462</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11186,6 +11646,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880475</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11320,6 +11785,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880500</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11454,6 +11924,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111880601</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11561,6 +12036,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157193</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11695,6 +12175,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129087801</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11802,6 +12287,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120153717</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11910,6 +12400,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285211</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12018,6 +12513,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285364</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12126,6 +12626,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285389</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12234,6 +12739,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108285502</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12331,6 +12841,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888935</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12451,6 +12966,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133055658</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12557,6 +13077,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126426462</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12654,6 +13179,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108861550</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12756,6 +13286,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888936</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12858,6 +13393,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888937</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12960,6 +13500,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112888940</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13071,6 +13616,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720201</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13182,6 +13732,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127720227</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13293,6 +13848,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128100976</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13404,6 +13964,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101030</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13515,6 +14080,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101112</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13626,6 +14196,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101132</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13737,6 +14312,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101236</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13848,6 +14428,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128200238</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13968,6 +14553,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133055527</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14075,6 +14665,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120155417</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14194,6 +14789,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129087869</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14305,6 +14905,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120159579</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14424,6 +15029,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88117465</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14550,6 +15160,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82056715</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14676,6 +15291,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82056744</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14791,6 +15411,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87425316</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14898,6 +15523,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120153346</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15005,6 +15635,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120153431</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15112,6 +15747,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120157228</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15217,6 +15857,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101422</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15324,6 +15969,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778187</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15431,6 +16081,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778197</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15538,6 +16193,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778208</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15645,6 +16305,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778231</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15752,6 +16417,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778275</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15859,6 +16529,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778283</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15978,6 +16653,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133101382</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16102,8 +16782,151 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507954</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ137"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11022,10 +11022,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88117320</v>
+        <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>90522</v>
+        <v>93362</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11033,37 +11033,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>509974</v>
+        <v>510041</v>
       </c>
       <c r="R89" t="n">
-        <v>6753133</v>
+        <v>6753064</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11090,12 +11087,27 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11104,82 +11116,77 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88117320</t>
+          <t>https://artportalen.se/Sighting/136114818</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>82056722</v>
+        <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>91282</v>
+        <v>93362</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Enån NR, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>509957</v>
+        <v>510038</v>
       </c>
       <c r="R90" t="n">
-        <v>6753178</v>
+        <v>6753069</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -11206,12 +11213,27 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11220,97 +11242,80 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>kalktallkog</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>gammal låga # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82056722</t>
+          <t>https://artportalen.se/Sighting/136114819</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119909303</v>
+        <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>91282</v>
+        <v>93362</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Lilla Kungsholstjärnen, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>509461</v>
+        <v>509818</v>
       </c>
       <c r="R91" t="n">
-        <v>6753296</v>
+        <v>6753590</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11334,12 +11339,27 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11354,27 +11374,27 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Richard Vestin</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Richard Vestin, Nicklas Johansson, Kristin Lundvall</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119909303</t>
+          <t>https://artportalen.se/Sighting/136114825</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>111880462</v>
+        <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>91443</v>
+        <v>93362</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11382,45 +11402,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5754</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>509970</v>
+        <v>509895</v>
       </c>
       <c r="R92" t="n">
-        <v>6753250</v>
+        <v>6753378</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11447,12 +11456,27 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Sandtallskog, kalk</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11461,64 +11485,33 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL92" t="inlineStr">
-        <is>
-          <t>vid tallar</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # vid tallar</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111880462</t>
+          <t>https://artportalen.se/Sighting/136114826</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>111880475</v>
+        <v>88117320</v>
       </c>
       <c r="B93" t="n">
-        <v>91443</v>
+        <v>90522</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11526,33 +11519,25 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5754</v>
+        <v>4962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
@@ -11561,10 +11546,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>509958</v>
+        <v>509974</v>
       </c>
       <c r="R93" t="n">
-        <v>6753363</v>
+        <v>6753133</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11591,12 +11576,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11619,21 +11604,6 @@
           <t>kalkmarksskog</t>
         </is>
       </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
@@ -11642,68 +11612,60 @@
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111880475</t>
+          <t>https://artportalen.se/Sighting/88117320</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>111880500</v>
+        <v>82056722</v>
       </c>
       <c r="B94" t="n">
-        <v>91443</v>
+        <v>91282</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5754</v>
+        <v>5685</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Enån NR, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>509899</v>
+        <v>509957</v>
       </c>
       <c r="R94" t="n">
-        <v>6753571</v>
+        <v>6753178</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11730,12 +11692,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11755,22 +11717,22 @@
       </c>
       <c r="AI94" t="inlineStr">
         <is>
-          <t>kalkmarksskog</t>
+          <t>kalktallkog</t>
         </is>
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>gammal låga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
@@ -11781,71 +11743,60 @@
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111880500</t>
+          <t>https://artportalen.se/Sighting/82056722</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>111880601</v>
+        <v>119909303</v>
       </c>
       <c r="B95" t="n">
-        <v>91443</v>
+        <v>91282</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5754</v>
+        <v>5685</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Lilla Kungsholstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>509941</v>
+        <v>509461</v>
       </c>
       <c r="R95" t="n">
-        <v>6753225</v>
+        <v>6753296</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11869,12 +11820,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-09-03</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11883,56 +11834,30 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Richard Vestin</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Richard Vestin, Nicklas Johansson, Kristin Lundvall</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111880601</t>
+          <t>https://artportalen.se/Sighting/119909303</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120157193</v>
+        <v>111880462</v>
       </c>
       <c r="B96" t="n">
         <v>91443</v>
@@ -11960,20 +11885,31 @@
           <t>(Bres.) Corner</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>509961</v>
+        <v>509970</v>
       </c>
       <c r="R96" t="n">
-        <v>6753330</v>
+        <v>6753250</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11997,22 +11933,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12021,30 +11947,61 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL96" t="inlineStr">
+        <is>
+          <t>vid tallar</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # vid tallar</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120157193</t>
+          <t>https://artportalen.se/Sighting/111880462</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129087801</v>
+        <v>111880475</v>
       </c>
       <c r="B97" t="n">
         <v>91443</v>
@@ -12090,10 +12047,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>509767</v>
+        <v>509958</v>
       </c>
       <c r="R97" t="n">
-        <v>6753551</v>
+        <v>6753363</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12120,12 +12077,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12145,7 +12102,7 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>kalkmark</t>
+          <t>kalkmarksskog</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -12177,54 +12134,65 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129087801</t>
+          <t>https://artportalen.se/Sighting/111880475</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120153717</v>
+        <v>111880500</v>
       </c>
       <c r="B98" t="n">
-        <v>90710</v>
+        <v>91443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6286</v>
+        <v>5754</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>509956</v>
+        <v>509899</v>
       </c>
       <c r="R98" t="n">
-        <v>6753135</v>
+        <v>6753571</v>
       </c>
       <c r="S98" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12248,22 +12216,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>12:59</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12272,72 +12230,108 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120153717</t>
+          <t>https://artportalen.se/Sighting/111880500</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>108285211</v>
+        <v>111880601</v>
       </c>
       <c r="B99" t="n">
-        <v>99153</v>
+        <v>91443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219874</v>
+        <v>5754</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>510131</v>
+        <v>509941</v>
       </c>
       <c r="R99" t="n">
-        <v>6753021</v>
+        <v>6753225</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12361,22 +12355,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>09:27</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12385,69 +12369,94 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108285211</t>
+          <t>https://artportalen.se/Sighting/111880601</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>108285364</v>
+        <v>120157193</v>
       </c>
       <c r="B100" t="n">
-        <v>99153</v>
+        <v>91443</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>219874</v>
+        <v>5754</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Dlr</t>
+          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>510048</v>
+        <v>509961</v>
       </c>
       <c r="R100" t="n">
-        <v>6753027</v>
+        <v>6753330</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12474,22 +12483,22 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12515,55 +12524,65 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108285364</t>
+          <t>https://artportalen.se/Sighting/120157193</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>108285389</v>
+        <v>129087801</v>
       </c>
       <c r="B101" t="n">
-        <v>99153</v>
+        <v>91443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219874</v>
+        <v>5754</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>510053</v>
+        <v>509767</v>
       </c>
       <c r="R101" t="n">
-        <v>6753075</v>
+        <v>6753551</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12587,22 +12606,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>09:33</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12611,69 +12620,94 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108285389</t>
+          <t>https://artportalen.se/Sighting/129087801</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>108285502</v>
+        <v>120153717</v>
       </c>
       <c r="B102" t="n">
-        <v>99153</v>
+        <v>90710</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219874</v>
+        <v>6286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärnen, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>509911</v>
+        <v>509956</v>
       </c>
       <c r="R102" t="n">
-        <v>6753260</v>
+        <v>6753135</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -12700,22 +12734,22 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-04-20</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12741,13 +12775,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108285502</t>
+          <t>https://artportalen.se/Sighting/120153717</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>112888935</v>
+        <v>108285211</v>
       </c>
       <c r="B103" t="n">
         <v>99153</v>
@@ -12776,16 +12810,17 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn SO om, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>509671</v>
+        <v>510131</v>
       </c>
       <c r="R103" t="n">
-        <v>6753153</v>
+        <v>6753021</v>
       </c>
       <c r="S103" t="n">
         <v>25</v>
@@ -12812,12 +12847,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>09:27</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12832,27 +12877,27 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112888935</t>
+          <t>https://artportalen.se/Sighting/108285211</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133055658</v>
+        <v>108285364</v>
       </c>
       <c r="B104" t="n">
-        <v>99230</v>
+        <v>99153</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12877,32 +12922,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>509909</v>
+        <v>510048</v>
       </c>
       <c r="R104" t="n">
-        <v>6753048</v>
+        <v>6753027</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12926,12 +12960,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12940,44 +12984,33 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>Sandtallskog med kalk</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133055658</t>
+          <t>https://artportalen.se/Sighting/108285364</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>126426462</v>
+        <v>108285389</v>
       </c>
       <c r="B105" t="n">
-        <v>99022</v>
+        <v>99153</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12985,45 +13018,38 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220093</v>
+        <v>219874</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>SMA Mineral, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>509954</v>
+        <v>510053</v>
       </c>
       <c r="R105" t="n">
-        <v>6752934</v>
+        <v>6753075</v>
       </c>
       <c r="S105" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13047,12 +13073,22 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13061,72 +13097,72 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126426462</t>
+          <t>https://artportalen.se/Sighting/108285389</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>108861550</v>
+        <v>108285502</v>
       </c>
       <c r="B106" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärnen, Rättvik, Dlr</t>
+          <t>Stora Kungsholstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>509554</v>
+        <v>509911</v>
       </c>
       <c r="R106" t="n">
-        <v>6753290</v>
+        <v>6753260</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13150,12 +13186,22 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2023-04-20</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -13170,66 +13216,62 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Carl Jansson, Andreas Öster, Lina Lejonberg, Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Niklas Trogen</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108861550</t>
+          <t>https://artportalen.se/Sighting/108285502</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>112888936</v>
+        <v>112888935</v>
       </c>
       <c r="B107" t="n">
-        <v>99118</v>
+        <v>99153</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Stora Kungsholstjärn SO om, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>509677</v>
+        <v>509671</v>
       </c>
       <c r="R107" t="n">
-        <v>6753149</v>
+        <v>6753153</v>
       </c>
       <c r="S107" t="n">
         <v>25</v>
@@ -13270,7 +13312,6 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
       </c>
@@ -13288,58 +13329,66 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112888936</t>
+          <t>https://artportalen.se/Sighting/112888935</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>112888937</v>
+        <v>133055658</v>
       </c>
       <c r="B108" t="n">
-        <v>99118</v>
+        <v>99230</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn SO om, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>509622</v>
+        <v>509909</v>
       </c>
       <c r="R108" t="n">
-        <v>6753141</v>
+        <v>6753048</v>
       </c>
       <c r="S108" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13363,12 +13412,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13381,72 +13430,87 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Sandtallskog med kalk</t>
+        </is>
+      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112888937</t>
+          <t>https://artportalen.se/Sighting/133055658</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>112888940</v>
+        <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99118</v>
+        <v>99328</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn SO om, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>510063</v>
+        <v>510035</v>
       </c>
       <c r="R109" t="n">
-        <v>6753044</v>
+        <v>6753066</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13470,12 +13534,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-05-03</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13484,80 +13563,71 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112888940</t>
+          <t>https://artportalen.se/Sighting/136114821</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>127720201</v>
+        <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99118</v>
+        <v>99328</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kungshol, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>509707</v>
+        <v>509928</v>
       </c>
       <c r="R110" t="n">
-        <v>6753556</v>
+        <v>6753231</v>
       </c>
       <c r="S110" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13581,17 +13651,27 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>En blomställning.</t>
+          <t>Kalksandskog</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13600,80 +13680,71 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127720201</t>
+          <t>https://artportalen.se/Sighting/136114827</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>127720227</v>
+        <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>99118</v>
+        <v>108055</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kungshol, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>509707</v>
+        <v>509956</v>
       </c>
       <c r="R111" t="n">
-        <v>6753444</v>
+        <v>6753343</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13697,17 +13768,27 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Tre blomställningar.</t>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13716,61 +13797,60 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127720227</t>
+          <t>https://artportalen.se/Sighting/136114824</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128100976</v>
+        <v>126426462</v>
       </c>
       <c r="B112" t="n">
-        <v>99118</v>
+        <v>99022</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>220093</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J112" t="inlineStr"/>
@@ -13779,17 +13859,17 @@
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>SMA Mineral, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>509761</v>
+        <v>509954</v>
       </c>
       <c r="R112" t="n">
-        <v>6753556</v>
+        <v>6752934</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13813,17 +13893,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>14 blomställningar.</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13850,13 +13925,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128100976</t>
+          <t>https://artportalen.se/Sighting/126426462</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128101030</v>
+        <v>108861550</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -13884,25 +13959,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärnen, Rättvik, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>509870</v>
+        <v>509554</v>
       </c>
       <c r="R113" t="n">
-        <v>6753445</v>
+        <v>6753290</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13929,17 +13996,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>1 blomställning.</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13948,31 +14010,30 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Carl Jansson, Andreas Öster, Lina Lejonberg, Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Niklas Trogen</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128101030</t>
+          <t>https://artportalen.se/Sighting/108861550</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128101112</v>
+        <v>112888936</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -14000,28 +14061,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
       <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärn SO om, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>509924</v>
+        <v>509677</v>
       </c>
       <c r="R114" t="n">
-        <v>6753445</v>
+        <v>6753149</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14045,17 +14102,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>7 Blomställningar.</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14071,24 +14123,24 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128101112</t>
+          <t>https://artportalen.se/Sighting/112888936</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128101132</v>
+        <v>112888937</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -14116,28 +14168,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärn SO om, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>509925</v>
+        <v>509622</v>
       </c>
       <c r="R115" t="n">
-        <v>6753222</v>
+        <v>6753141</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14161,17 +14209,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>11 blomställningar.</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14187,24 +14230,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128101132</t>
+          <t>https://artportalen.se/Sighting/112888937</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128101236</v>
+        <v>112888940</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -14232,28 +14275,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärn SO om, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>509762</v>
+        <v>510063</v>
       </c>
       <c r="R116" t="n">
-        <v>6753222</v>
+        <v>6753044</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14277,17 +14316,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>4 blomställningar.</t>
+          <t>2023-05-03</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14303,24 +14337,24 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Veronica Jägbrant, Jenny Andersson, Ulf Lindenbaum, Carl Jansson, Andreas Öster, Lina Lejonberg</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128101236</t>
+          <t>https://artportalen.se/Sighting/112888940</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128200238</v>
+        <v>127720201</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -14350,7 +14384,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
@@ -14359,17 +14393,17 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Kungshol, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>509905</v>
+        <v>509707</v>
       </c>
       <c r="R117" t="n">
-        <v>6752956</v>
+        <v>6753556</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14393,17 +14427,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>Sex blomställningar.</t>
+          <t>En blomställning.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14430,16 +14464,16 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128200238</t>
+          <t>https://artportalen.se/Sighting/127720201</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133055527</v>
+        <v>127720227</v>
       </c>
       <c r="B118" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14469,24 +14503,20 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Kungshol, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>509716</v>
+        <v>509707</v>
       </c>
       <c r="R118" t="n">
-        <v>6753197</v>
+        <v>6753444</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14513,12 +14543,17 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Tre blomställningar.</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14531,78 +14566,76 @@
       <c r="AG118" t="b">
         <v>0</v>
       </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>Sandtallskog med kalk</t>
-        </is>
-      </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133055527</t>
+          <t>https://artportalen.se/Sighting/127720227</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120155417</v>
+        <v>128100976</v>
       </c>
       <c r="B119" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>509869</v>
+        <v>509761</v>
       </c>
       <c r="R119" t="n">
-        <v>6753545</v>
+        <v>6753556</v>
       </c>
       <c r="S119" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14626,22 +14659,17 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>13:11</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>14 blomställningar.</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14650,55 +14678,56 @@
       <c r="AE119" t="b">
         <v>0</v>
       </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120155417</t>
+          <t>https://artportalen.se/Sighting/128100976</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129087869</v>
+        <v>128101030</v>
       </c>
       <c r="B120" t="n">
-        <v>89073</v>
+        <v>99118</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>239200</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spetsvaxing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hygrocybe acutoconica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Clem.) Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -14706,26 +14735,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>509627</v>
+        <v>509870</v>
       </c>
       <c r="R120" t="n">
-        <v>6753144</v>
+        <v>6753445</v>
       </c>
       <c r="S120" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -14749,12 +14775,17 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>1 blomställning.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14767,40 +14798,30 @@
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>kalkmark</t>
-        </is>
-      </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129087869</t>
+          <t>https://artportalen.se/Sighting/128101030</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120159579</v>
+        <v>128101112</v>
       </c>
       <c r="B121" t="n">
-        <v>87291</v>
+        <v>99118</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14808,40 +14829,45 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>248955</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tvillingspindling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Cortinarius metarius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Kauffman</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>509849</v>
+        <v>509924</v>
       </c>
       <c r="R121" t="n">
-        <v>6753083</v>
+        <v>6753445</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14865,22 +14891,17 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>14:26</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>7 Blomställningar.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14896,76 +14917,73 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120159579</t>
+          <t>https://artportalen.se/Sighting/128101112</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>88117465</v>
+        <v>128101132</v>
       </c>
       <c r="B122" t="n">
-        <v>91402</v>
+        <v>99118</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>510027</v>
+        <v>509925</v>
       </c>
       <c r="R122" t="n">
-        <v>6752975</v>
+        <v>6753222</v>
       </c>
       <c r="S122" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14989,12 +15007,17 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2020-09-17</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>11 blomställningar.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15007,81 +15030,76 @@
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>kalkmarksskog</t>
-        </is>
-      </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88117465</t>
+          <t>https://artportalen.se/Sighting/128101132</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>82056715</v>
+        <v>128101236</v>
       </c>
       <c r="B123" t="n">
-        <v>79350</v>
+        <v>99118</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>509929</v>
+        <v>509762</v>
       </c>
       <c r="R123" t="n">
-        <v>6753367</v>
+        <v>6753222</v>
       </c>
       <c r="S123" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -15105,12 +15123,17 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2025-08-27</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>4 blomställningar.</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -15123,96 +15146,76 @@
       <c r="AG123" t="b">
         <v>0</v>
       </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>kalktallkog</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82056715</t>
+          <t>https://artportalen.se/Sighting/128101236</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>82056744</v>
+        <v>128200238</v>
       </c>
       <c r="B124" t="n">
-        <v>79350</v>
+        <v>99118</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>260591</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>509951</v>
+        <v>509905</v>
       </c>
       <c r="R124" t="n">
-        <v>6753233</v>
+        <v>6752956</v>
       </c>
       <c r="S124" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -15236,12 +15239,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2020-02-05</t>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Sex blomställningar.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -15254,97 +15262,77 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>kalktallkog</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82056744</t>
+          <t>https://artportalen.se/Sighting/128200238</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>87425316</v>
+        <v>133055527</v>
       </c>
       <c r="B125" t="n">
-        <v>93202</v>
+        <v>99195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6003298</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Kalkbruket, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>509840</v>
+        <v>509716</v>
       </c>
       <c r="R125" t="n">
-        <v>6753012</v>
+        <v>6753197</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15371,12 +15359,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2020-08-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15396,71 +15384,71 @@
       </c>
       <c r="AI125" t="inlineStr">
         <is>
-          <t>Klen tallskog på kalkhaltig sandjord.</t>
+          <t>Sandtallskog med kalk</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87425316</t>
+          <t>https://artportalen.se/Sighting/133055527</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120153346</v>
+        <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>93202</v>
+        <v>106433</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6003298</v>
+        <v>221144</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>510057</v>
+        <v>510041</v>
       </c>
       <c r="R126" t="n">
-        <v>6753057</v>
+        <v>6753064</v>
       </c>
       <c r="S126" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -15484,22 +15472,27 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:24</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15514,62 +15507,62 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120153346</t>
+          <t>https://artportalen.se/Sighting/136114817</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120153431</v>
+        <v>120155417</v>
       </c>
       <c r="B127" t="n">
-        <v>93202</v>
+        <v>97989</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6003298</v>
+        <v>221941</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
+          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>510035</v>
+        <v>509869</v>
       </c>
       <c r="R127" t="n">
-        <v>6753057</v>
+        <v>6753545</v>
       </c>
       <c r="S127" t="n">
         <v>25</v>
@@ -15601,7 +15594,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15611,7 +15604,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15637,54 +15630,65 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120153431</t>
+          <t>https://artportalen.se/Sighting/120155417</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120157228</v>
+        <v>129087869</v>
       </c>
       <c r="B128" t="n">
-        <v>93202</v>
+        <v>89073</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6003298</v>
+        <v>239200</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Spetsvaxing</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Hygrocybe acutoconica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>(Clem.) Singer</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>509982</v>
+        <v>509627</v>
       </c>
       <c r="R128" t="n">
-        <v>6753276</v>
+        <v>6753144</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -15708,22 +15712,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15732,78 +15726,85 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>kalkmark</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson, Nadja Hermansson Kovler</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120157228</t>
+          <t>https://artportalen.se/Sighting/129087869</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128101422</v>
+        <v>120159579</v>
       </c>
       <c r="B129" t="n">
-        <v>93202</v>
+        <v>87291</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6003298</v>
+        <v>248955</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Tvillingspindling</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Cortinarius metarius</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Kauffman</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>509925</v>
+        <v>509849</v>
       </c>
       <c r="R129" t="n">
-        <v>6753111</v>
+        <v>6753083</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15827,12 +15828,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15848,65 +15859,76 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Emma Billbäck</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128101422</t>
+          <t>https://artportalen.se/Sighting/120159579</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128778187</v>
+        <v>88117465</v>
       </c>
       <c r="B130" t="n">
-        <v>93202</v>
+        <v>91402</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6003298</v>
+        <v>256703</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>509958</v>
+        <v>510027</v>
       </c>
       <c r="R130" t="n">
-        <v>6753025</v>
+        <v>6752975</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -15930,22 +15952,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z130" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB130" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-09-17</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15954,71 +15966,85 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>kalkmarksskog</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778187</t>
+          <t>https://artportalen.se/Sighting/88117465</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128778197</v>
+        <v>82056715</v>
       </c>
       <c r="B131" t="n">
-        <v>93202</v>
+        <v>79350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6003298</v>
+        <v>260591</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>509961</v>
+        <v>509929</v>
       </c>
       <c r="R131" t="n">
-        <v>6753014</v>
+        <v>6753367</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -16042,22 +16068,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -16066,71 +16082,100 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>kalktallkog</t>
+        </is>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778197</t>
+          <t>https://artportalen.se/Sighting/82056715</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128778208</v>
+        <v>82056744</v>
       </c>
       <c r="B132" t="n">
-        <v>93202</v>
+        <v>79350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6003298</v>
+        <v>260591</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ruttaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum illudens</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Maas Geest.) Nitare</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Rättviksheden, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>509955</v>
+        <v>509951</v>
       </c>
       <c r="R132" t="n">
-        <v>6753010</v>
+        <v>6753233</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16154,22 +16199,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-02-05</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16178,30 +16213,56 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>kalktallkog</t>
+        </is>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Janolof Hermansson</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778208</t>
+          <t>https://artportalen.se/Sighting/82056744</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128778231</v>
+        <v>87425316</v>
       </c>
       <c r="B133" t="n">
         <v>93202</v>
@@ -16229,17 +16290,24 @@
           <t>(Maas Geest.) Nitare</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Kalkbruket, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>510008</v>
+        <v>509840</v>
       </c>
       <c r="R133" t="n">
-        <v>6752986</v>
+        <v>6753012</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16266,22 +16334,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>11:28</t>
+          <t>2020-08-12</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16290,30 +16348,41 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AH133" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>Klen tallskog på kalkhaltig sandjord.</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778231</t>
+          <t>https://artportalen.se/Sighting/87425316</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128778275</v>
+        <v>120153346</v>
       </c>
       <c r="B134" t="n">
         <v>93202</v>
@@ -16344,17 +16413,17 @@
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>510063</v>
+        <v>510057</v>
       </c>
       <c r="R134" t="n">
-        <v>6752946</v>
+        <v>6753057</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16378,22 +16447,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16419,13 +16488,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778275</t>
+          <t>https://artportalen.se/Sighting/120153346</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128778283</v>
+        <v>120153431</v>
       </c>
       <c r="B135" t="n">
         <v>93202</v>
@@ -16456,17 +16525,17 @@
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+          <t>Gärdsgruvans naturreservat, Gärdsgruvans naturreservat, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>510086</v>
+        <v>510035</v>
       </c>
       <c r="R135" t="n">
-        <v>6752923</v>
+        <v>6753057</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16490,22 +16559,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16531,16 +16600,16 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128778283</t>
+          <t>https://artportalen.se/Sighting/120153431</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133101382</v>
+        <v>120157228</v>
       </c>
       <c r="B136" t="n">
-        <v>93276</v>
+        <v>93202</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16565,31 +16634,20 @@
           <t>(Maas Geest.) Nitare</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Stora Kungsholstjärn, Dlr</t>
+          <t>Stora Kungsholstjärnen, Stora Kungsholstjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>509957</v>
+        <v>509982</v>
       </c>
       <c r="R136" t="n">
-        <v>6753118</v>
+        <v>6753276</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -16613,12 +16671,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16627,93 +16695,78 @@
       <c r="AE136" t="b">
         <v>0</v>
       </c>
-      <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="b">
         <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>Sandskog</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>Kalkhaltig sandbarrskog, mest tall</t>
-        </is>
       </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133101382</t>
+          <t>https://artportalen.se/Sighting/120157228</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>112507954</v>
+        <v>128101422</v>
       </c>
       <c r="B137" t="n">
-        <v>92328</v>
+        <v>93202</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6040162</v>
+        <v>6003298</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Ruttaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum illudens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Maas Geest.) Nitare</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J137" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>509423</v>
+        <v>509925</v>
       </c>
       <c r="R137" t="n">
-        <v>6753247</v>
+        <v>6753111</v>
       </c>
       <c r="S137" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16737,12 +16790,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16755,34 +16808,1325 @@
       <c r="AG137" t="b">
         <v>0</v>
       </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>med granar, kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>högstubbe på hygge</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Emma Billbäck</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128101422</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>128778187</v>
+      </c>
+      <c r="B138" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>509958</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6753025</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778187</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>128778197</v>
+      </c>
+      <c r="B139" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>509961</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6753014</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778197</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>128778208</v>
+      </c>
+      <c r="B140" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>509955</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6753010</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778208</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>128778231</v>
+      </c>
+      <c r="B141" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>510008</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6752986</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778231</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>128778275</v>
+      </c>
+      <c r="B142" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>510063</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6752946</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778275</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>128778283</v>
+      </c>
+      <c r="B143" t="n">
+        <v>93202</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>St Kungsholstjärn, St Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>510086</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6752923</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128778283</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>133101382</v>
+      </c>
+      <c r="B144" t="n">
+        <v>93276</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Stora Kungsholstjärn, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>509957</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6753118</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Sandskog</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>Kalkhaltig sandbarrskog, mest tall</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133101382</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>136114820</v>
+      </c>
+      <c r="B145" t="n">
+        <v>93367</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Kalk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>510035</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6753064</v>
+      </c>
+      <c r="S145" t="n">
+        <v>5</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114820</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>136114822</v>
+      </c>
+      <c r="B146" t="n">
+        <v>93367</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Kalk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>510026</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6753073</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114822</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>136114823</v>
+      </c>
+      <c r="B147" t="n">
+        <v>93367</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Kalk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>510003</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6753100</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114823</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>112507954</v>
+      </c>
+      <c r="B148" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Rättviksheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>509423</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6753247</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>med granar, kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>högstubbe på hygge</t>
+        </is>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112507954</t>
         </is>
@@ -16926,6 +18270,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99328</v>
+        <v>99329</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13617,7 +13617,7 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108055</v>
+        <v>108057</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106433</v>
+        <v>106435</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Kalk, Dlr</t>
+          <t>Stora Kungsholstjärn, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99329</v>
+        <v>99330</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108057</v>
+        <v>108058</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106435</v>
+        <v>106436</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99330</v>
+        <v>99331</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108058</v>
+        <v>108059</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106436</v>
+        <v>106437</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99331</v>
+        <v>99337</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108059</v>
+        <v>108065</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106437</v>
+        <v>106443</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93370</v>
+        <v>93376</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93370</v>
+        <v>93376</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93370</v>
+        <v>93376</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99337</v>
+        <v>99338</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108065</v>
+        <v>108066</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106443</v>
+        <v>106444</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93376</v>
+        <v>93377</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93376</v>
+        <v>93377</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93376</v>
+        <v>93377</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -11025,7 +11025,7 @@
         <v>136114818</v>
       </c>
       <c r="B89" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>136114819</v>
       </c>
       <c r="B90" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11268,7 +11268,7 @@
         <v>136114825</v>
       </c>
       <c r="B91" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>136114826</v>
       </c>
       <c r="B92" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13463,7 +13463,7 @@
         <v>136114821</v>
       </c>
       <c r="B109" t="n">
-        <v>99338</v>
+        <v>99349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>136114827</v>
       </c>
       <c r="B110" t="n">
-        <v>99338</v>
+        <v>99349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>136114824</v>
       </c>
       <c r="B111" t="n">
-        <v>108066</v>
+        <v>108077</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>136114817</v>
       </c>
       <c r="B126" t="n">
-        <v>106444</v>
+        <v>106455</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         <v>136114820</v>
       </c>
       <c r="B145" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>136114822</v>
       </c>
       <c r="B146" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>136114823</v>
       </c>
       <c r="B147" t="n">
-        <v>93377</v>
+        <v>93383</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ157"/>
+  <dimension ref="A1:AZ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101556</v>
+        <v>101557</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99362</v>
+        <v>99363</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99362</v>
+        <v>99363</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99362</v>
+        <v>99363</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108090</v>
+        <v>108091</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106468</v>
+        <v>106469</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93390</v>
+        <v>93391</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93390</v>
+        <v>93391</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93390</v>
+        <v>93391</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93390</v>
+        <v>93391</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93390</v>
+        <v>93391</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18837,56 +18837,54 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>112507954</v>
+        <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>92328</v>
+        <v>93391</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6040162</v>
+        <v>6003298</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Ruttaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum illudens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Maas Geest.) Nitare</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Rättviksheden, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>509423</v>
+        <v>510089</v>
       </c>
       <c r="R156" t="n">
-        <v>6753247</v>
+        <v>6753031</v>
       </c>
       <c r="S156" t="n">
         <v>5</v>
@@ -18913,12 +18911,27 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18927,87 +18940,71 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Sandtallskog</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>med granar, kalkmarksskog</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>högstubbe på hygge</t>
-        </is>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Janolof Hermansson</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112507954</t>
+          <t>https://artportalen.se/Sighting/136431854</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>136378990</v>
+        <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93413</v>
+        <v>93391</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6332770</v>
+        <v>6003298</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ruttaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum illudens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) P.Karst.</t>
+          <t>(Maas Geest.) Nitare</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Gärdsgruvans naturreservat, Dlr</t>
+          <t>Kalk, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>510007</v>
+        <v>510053</v>
       </c>
       <c r="R157" t="n">
-        <v>6753082</v>
+        <v>6753064</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -19034,9 +19031,24 @@
           <t>2026-09-06</t>
         </is>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -19051,16 +19063,481 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136431855</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>136431856</v>
+      </c>
+      <c r="B158" t="n">
+        <v>93391</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Kalk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>510006</v>
+      </c>
+      <c r="R158" t="n">
+        <v>6753081</v>
+      </c>
+      <c r="S158" t="n">
+        <v>5</v>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG158" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="inlineStr"/>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136431856</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>136431857</v>
+      </c>
+      <c r="B159" t="n">
+        <v>93391</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6003298</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Ruttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Hydnellum illudens</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Maas Geest.) Nitare</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Kalk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>509988</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6753110</v>
+      </c>
+      <c r="S159" t="n">
+        <v>5</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136431857</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>112507954</v>
+      </c>
+      <c r="B160" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Rättviksheden, Dlr</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>509423</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6753247</v>
+      </c>
+      <c r="S160" t="n">
+        <v>5</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2023-10-03</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>med granar, kalkmarksskog</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>högstubbe på hygge</t>
+        </is>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Janolof Hermansson</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112507954</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>136378990</v>
+      </c>
+      <c r="B161" t="n">
+        <v>93414</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Gärdsgruvans naturreservat, Dlr</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>510007</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6753082</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136378990</t>
         </is>
@@ -19224,6 +19701,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101557</v>
+        <v>101570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99363</v>
+        <v>99376</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106469</v>
+        <v>106482</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93391</v>
+        <v>93404</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93414</v>
+        <v>93427</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 777-2025 artfynd.xlsx
+++ b/artfynd/S 777-2025 artfynd.xlsx
@@ -5624,7 +5624,7 @@
         <v>136379145</v>
       </c>
       <c r="B44" t="n">
-        <v>101570</v>
+        <v>101571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>136114818</v>
       </c>
       <c r="B90" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>136114819</v>
       </c>
       <c r="B91" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11370,7 +11370,7 @@
         <v>136114825</v>
       </c>
       <c r="B92" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>136114826</v>
       </c>
       <c r="B93" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11613,7 +11613,7 @@
         <v>136377416</v>
       </c>
       <c r="B94" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>136377629</v>
       </c>
       <c r="B95" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>136114821</v>
       </c>
       <c r="B112" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13903,7 +13903,7 @@
         <v>136114827</v>
       </c>
       <c r="B113" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>136376346</v>
       </c>
       <c r="B114" t="n">
-        <v>99376</v>
+        <v>99377</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>136114824</v>
       </c>
       <c r="B115" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>136376641</v>
       </c>
       <c r="B130" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>136114817</v>
       </c>
       <c r="B131" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>136376838</v>
       </c>
       <c r="B132" t="n">
-        <v>106482</v>
+        <v>106483</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>136114820</v>
       </c>
       <c r="B151" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18381,7 +18381,7 @@
         <v>136114822</v>
       </c>
       <c r="B152" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18507,7 +18507,7 @@
         <v>136114823</v>
       </c>
       <c r="B153" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>136376375</v>
       </c>
       <c r="B154" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18738,7 +18738,7 @@
         <v>136376742</v>
       </c>
       <c r="B155" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>136431854</v>
       </c>
       <c r="B156" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>136431855</v>
       </c>
       <c r="B157" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>136431856</v>
       </c>
       <c r="B158" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19200,7 +19200,7 @@
         <v>136431857</v>
       </c>
       <c r="B159" t="n">
-        <v>93404</v>
+        <v>93405</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         <v>136378990</v>
       </c>
       <c r="B161" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
